--- a/fact_ventas/outputs/06_historial_entrenamiento.xlsx
+++ b/fact_ventas/outputs/06_historial_entrenamiento.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.9772019836380934</v>
+        <v>0.9772019836380932</v>
       </c>
       <c r="C16" t="n">
         <v>0.9670796255277871</v>
@@ -737,7 +737,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.9548563491767411</v>
+        <v>0.9548563491767413</v>
       </c>
       <c r="C19" t="n">
         <v>0.9448812291562728</v>
@@ -754,7 +754,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.947866850809059</v>
+        <v>0.9478668508090591</v>
       </c>
       <c r="C20" t="n">
         <v>0.9379204120880719</v>
@@ -822,7 +822,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9219028919396576</v>
+        <v>0.9219028919396575</v>
       </c>
       <c r="C24" t="n">
         <v>0.9119957693657815</v>
@@ -856,10 +856,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.9099951796971277</v>
+        <v>0.9099951796971278</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9000722678748202</v>
+        <v>0.9000722678748203</v>
       </c>
       <c r="D26" t="n">
         <v>0.6113653478537914</v>
@@ -873,7 +873,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.9042845402026219</v>
+        <v>0.9042845402026221</v>
       </c>
       <c r="C27" t="n">
         <v>0.8943467349298044</v>
@@ -907,7 +907,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.893319711487673</v>
+        <v>0.8933197114876729</v>
       </c>
       <c r="C29" t="n">
         <v>0.8833400738480371</v>
@@ -924,7 +924,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8880547608564571</v>
+        <v>0.8880547608564572</v>
       </c>
       <c r="C30" t="n">
         <v>0.8780488245969141</v>
@@ -941,10 +941,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8829281696000604</v>
+        <v>0.8829281696000605</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8728927100823997</v>
+        <v>0.8728927100823995</v>
       </c>
       <c r="D31" t="n">
         <v>0.6128714591901755</v>
@@ -975,7 +975,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8730718626930322</v>
+        <v>0.8730718626930324</v>
       </c>
       <c r="C33" t="n">
         <v>0.8629685902606404</v>
@@ -992,7 +992,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.8683336101781368</v>
+        <v>0.8683336101781367</v>
       </c>
       <c r="C34" t="n">
         <v>0.8581924407762007</v>
@@ -1026,7 +1026,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.8592169727478307</v>
+        <v>0.8592169727478306</v>
       </c>
       <c r="C36" t="n">
         <v>0.8489928642342955</v>
@@ -1060,7 +1060,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.8505553764766103</v>
+        <v>0.8505553764766102</v>
       </c>
       <c r="C38" t="n">
         <v>0.840239742890924</v>
@@ -1094,7 +1094,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.8423208433561161</v>
+        <v>0.842320843356116</v>
       </c>
       <c r="C40" t="n">
         <v>0.8319060754370722</v>
@@ -1128,7 +1128,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.8344870868130029</v>
+        <v>0.834487086813003</v>
       </c>
       <c r="C42" t="n">
         <v>0.8239664251097744</v>
@@ -1145,7 +1145,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.8307126845185213</v>
+        <v>0.8307126845185212</v>
       </c>
       <c r="C43" t="n">
         <v>0.8201367816741315</v>
@@ -1162,7 +1162,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.8270292625316095</v>
+        <v>0.8270292625316094</v>
       </c>
       <c r="C44" t="n">
         <v>0.8163967087688035</v>
@@ -1179,7 +1179,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.8234339137604321</v>
+        <v>0.823433913760432</v>
       </c>
       <c r="C45" t="n">
         <v>0.8127433848943361</v>
@@ -1247,7 +1247,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.8098776161530896</v>
+        <v>0.8098776161530895</v>
       </c>
       <c r="C49" t="n">
         <v>0.7989435673129976</v>
@@ -1264,7 +1264,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.8066815078969397</v>
+        <v>0.8066815078969398</v>
       </c>
       <c r="C50" t="n">
         <v>0.7956840615195437</v>
@@ -1298,7 +1298,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>0.8005031465245217</v>
+        <v>0.8005031465245216</v>
       </c>
       <c r="C52" t="n">
         <v>0.7893764019092631</v>
@@ -1315,7 +1315,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>0.7975160930180142</v>
+        <v>0.7975160930180141</v>
       </c>
       <c r="C53" t="n">
         <v>0.7863235894866222</v>
@@ -1332,7 +1332,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>0.7945940292467459</v>
+        <v>0.7945940292467458</v>
       </c>
       <c r="C54" t="n">
         <v>0.7833351190371398</v>
@@ -1366,7 +1366,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7889359590084578</v>
+        <v>0.7889359590084577</v>
       </c>
       <c r="C56" t="n">
         <v>0.7775425598411274</v>
@@ -1383,10 +1383,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>0.7861956498615229</v>
+        <v>0.786195649861523</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7747342986372598</v>
+        <v>0.77473429863726</v>
       </c>
       <c r="D57" t="n">
         <v>0.6221977640039391</v>
@@ -1400,7 +1400,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>0.783511723764823</v>
+        <v>0.7835117237648231</v>
       </c>
       <c r="C58" t="n">
         <v>0.7719820331278381</v>
@@ -1485,7 +1485,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>0.770869840711556</v>
+        <v>0.7708698407115557</v>
       </c>
       <c r="C63" t="n">
         <v>0.7589947372173383</v>
@@ -1502,7 +1502,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>0.7684842182466119</v>
+        <v>0.7684842182466118</v>
       </c>
       <c r="C64" t="n">
         <v>0.7565396858479563</v>
@@ -1536,7 +1536,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>0.7638421060670287</v>
+        <v>0.7638421060670286</v>
       </c>
       <c r="C66" t="n">
         <v>0.7517587938227853</v>
@@ -1573,7 +1573,7 @@
         <v>0.7593617113321597</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7471400491294393</v>
+        <v>0.7471400491294394</v>
       </c>
       <c r="D68" t="n">
         <v>0.6735793315182761</v>
@@ -1587,7 +1587,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>0.7571784275634292</v>
+        <v>0.7571784275634293</v>
       </c>
       <c r="C69" t="n">
         <v>0.7448878675302393</v>
@@ -1624,7 +1624,7 @@
         <v>0.7529186583978877</v>
       </c>
       <c r="C71" t="n">
-        <v>0.7404910742384886</v>
+        <v>0.7404910742384887</v>
       </c>
       <c r="D71" t="n">
         <v>0.7238023518507791</v>
@@ -1638,7 +1638,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>0.7508395040826589</v>
+        <v>0.750839504082659</v>
       </c>
       <c r="C72" t="n">
         <v>0.7383438755376525</v>
@@ -1689,7 +1689,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>0.7447899025975501</v>
+        <v>0.7447899025975502</v>
       </c>
       <c r="C75" t="n">
         <v>0.7320924687198814</v>
@@ -1706,7 +1706,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>0.742832059956592</v>
+        <v>0.7428320599565919</v>
       </c>
       <c r="C76" t="n">
         <v>0.7300682511978741</v>
@@ -1723,7 +1723,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.7409017023517523</v>
+        <v>0.7409017023517525</v>
       </c>
       <c r="C77" t="n">
         <v>0.7280720203924413</v>
@@ -1757,7 +1757,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>0.7371192552204202</v>
+        <v>0.7371192552204201</v>
       </c>
       <c r="C79" t="n">
         <v>0.7241594530212339</v>
@@ -1774,7 +1774,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>0.7352651669391552</v>
+        <v>0.7352651669391551</v>
       </c>
       <c r="C80" t="n">
         <v>0.7222411745862681</v>
@@ -1808,7 +1808,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>0.7316265364169383</v>
+        <v>0.7316265364169384</v>
       </c>
       <c r="C82" t="n">
         <v>0.7184760352338057</v>
@@ -1825,7 +1825,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>0.7298402086362965</v>
+        <v>0.7298402086362964</v>
       </c>
       <c r="C83" t="n">
         <v>0.716627437274673</v>
@@ -1893,7 +1893,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>0.7228955043941915</v>
+        <v>0.7228955043941916</v>
       </c>
       <c r="C87" t="n">
         <v>0.7094407190352315</v>
@@ -1910,10 +1910,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>0.7212056497177389</v>
+        <v>0.7212056497177388</v>
       </c>
       <c r="C88" t="n">
-        <v>0.7076922234537166</v>
+        <v>0.7076922234537165</v>
       </c>
       <c r="D88" t="n">
         <v>0.7485952615420263</v>
@@ -1927,7 +1927,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>0.7195328928022365</v>
+        <v>0.7195328928022366</v>
       </c>
       <c r="C89" t="n">
         <v>0.7059616049582244</v>
@@ -1944,10 +1944,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>0.7178765662544188</v>
+        <v>0.7178765662544186</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7042482113643944</v>
+        <v>0.7042482113643943</v>
       </c>
       <c r="D90" t="n">
         <v>0.7492903898511267</v>
@@ -1978,7 +1978,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>0.7146106636502194</v>
+        <v>0.7146106636502195</v>
       </c>
       <c r="C92" t="n">
         <v>0.7008706139090276</v>
@@ -1995,7 +1995,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.7129998791683518</v>
+        <v>0.7129998791683519</v>
       </c>
       <c r="C93" t="n">
         <v>0.6992052269511068</v>
@@ -2114,10 +2114,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>0.7020876287396213</v>
+        <v>0.7020876287396212</v>
       </c>
       <c r="C100" t="n">
-        <v>0.6879349458768436</v>
+        <v>0.6879349458768435</v>
       </c>
       <c r="D100" t="n">
         <v>0.7491745351329433</v>
@@ -2131,7 +2131,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>0.700574822119484</v>
+        <v>0.7005748221194841</v>
       </c>
       <c r="C101" t="n">
         <v>0.6863745415670095</v>
@@ -2165,7 +2165,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>0.6975794631323681</v>
+        <v>0.6975794631323682</v>
       </c>
       <c r="C103" t="n">
         <v>0.6832867072090942</v>
@@ -2182,10 +2182,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>0.696096145612044</v>
+        <v>0.6960961456120441</v>
       </c>
       <c r="C104" t="n">
-        <v>0.6817585198097115</v>
+        <v>0.6817585198097116</v>
       </c>
       <c r="D104" t="n">
         <v>0.7491166077738516</v>
@@ -2199,7 +2199,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>0.6946219196283056</v>
+        <v>0.6946219196283057</v>
       </c>
       <c r="C105" t="n">
         <v>0.6802403399843749</v>
@@ -2284,7 +2284,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>0.6873756716133779</v>
+        <v>0.6873756716133778</v>
       </c>
       <c r="C110" t="n">
         <v>0.6727881275992865</v>
@@ -2318,7 +2318,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>0.6845299107753848</v>
+        <v>0.6845299107753847</v>
       </c>
       <c r="C112" t="n">
         <v>0.669866435560446</v>
@@ -2338,7 +2338,7 @@
         <v>0.683117262124688</v>
       </c>
       <c r="C113" t="n">
-        <v>0.6684172027175086</v>
+        <v>0.6684172027175085</v>
       </c>
       <c r="D113" t="n">
         <v>0.7498696634420436</v>
@@ -2352,7 +2352,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>0.6817111148783961</v>
+        <v>0.681711114878396</v>
       </c>
       <c r="C114" t="n">
         <v>0.6669753903145293</v>
@@ -2403,10 +2403,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>0.6775294802861183</v>
+        <v>0.6775294802861181</v>
       </c>
       <c r="C117" t="n">
-        <v>0.6626922531371104</v>
+        <v>0.6626922531371106</v>
       </c>
       <c r="D117" t="n">
         <v>0.7508544285466026</v>
@@ -2474,7 +2474,7 @@
         <v>0.67203251124144</v>
       </c>
       <c r="C121" t="n">
-        <v>0.6570726533798277</v>
+        <v>0.6570726533798276</v>
       </c>
       <c r="D121" t="n">
         <v>0.7516074842147946</v>
@@ -2488,10 +2488,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>0.6706711307230621</v>
+        <v>0.6706711307230618</v>
       </c>
       <c r="C122" t="n">
-        <v>0.6556828592370387</v>
+        <v>0.655682859237039</v>
       </c>
       <c r="D122" t="n">
         <v>0.751723338932978</v>
@@ -2573,7 +2573,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>0.6639341172525418</v>
+        <v>0.6639341172525417</v>
       </c>
       <c r="C127" t="n">
         <v>0.6488170054041705</v>
@@ -2624,7 +2624,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>0.659943514859012</v>
+        <v>0.6599435148590121</v>
       </c>
       <c r="C130" t="n">
         <v>0.6447594787692955</v>
@@ -2675,7 +2675,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>0.655988382049432</v>
+        <v>0.6559883820494321</v>
       </c>
       <c r="C133" t="n">
         <v>0.6407449972471958</v>
@@ -2692,7 +2692,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>0.6546775213605003</v>
+        <v>0.6546775213605004</v>
       </c>
       <c r="C134" t="n">
         <v>0.63941600437421</v>
@@ -2712,7 +2712,7 @@
         <v>0.6533703087630649</v>
       </c>
       <c r="C135" t="n">
-        <v>0.6380914725852507</v>
+        <v>0.6380914725852506</v>
       </c>
       <c r="D135" t="n">
         <v>0.7532873776284539</v>
@@ -2811,7 +2811,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>0.6456007759054788</v>
+        <v>0.6456007759054789</v>
       </c>
       <c r="C141" t="n">
         <v>0.6302346532827259</v>
@@ -2828,7 +2828,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>0.644317771608295</v>
+        <v>0.6443177716082948</v>
       </c>
       <c r="C142" t="n">
         <v>0.6289397950649531</v>
@@ -2845,10 +2845,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>0.643038093891151</v>
+        <v>0.6430380938911511</v>
       </c>
       <c r="C143" t="n">
-        <v>0.6276490099441171</v>
+        <v>0.627649009944117</v>
       </c>
       <c r="D143" t="n">
         <v>0.7544459248102879</v>
@@ -2913,7 +2913,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>0.6379523130400464</v>
+        <v>0.6379523130400465</v>
       </c>
       <c r="C147" t="n">
         <v>0.6225260821872474</v>
@@ -2947,7 +2947,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>0.6354290511629437</v>
+        <v>0.6354290511629436</v>
       </c>
       <c r="C149" t="n">
         <v>0.6199884850048627</v>
@@ -2981,7 +2981,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>0.6329188595802386</v>
+        <v>0.6329188595802387</v>
       </c>
       <c r="C151" t="n">
         <v>0.6174666803820732</v>
@@ -3035,7 +3035,7 @@
         <v>0.6291782038492472</v>
       </c>
       <c r="C154" t="n">
-        <v>0.6137135346190821</v>
+        <v>0.6137135346190822</v>
       </c>
       <c r="D154" t="n">
         <v>0.7560678908648555</v>
@@ -3049,7 +3049,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>0.6279379378518979</v>
+        <v>0.6279379378518978</v>
       </c>
       <c r="C155" t="n">
         <v>0.6124703790648414</v>
@@ -3069,7 +3069,7 @@
         <v>0.6267010100631921</v>
       </c>
       <c r="C156" t="n">
-        <v>0.6112311813587508</v>
+        <v>0.6112311813587509</v>
       </c>
       <c r="D156" t="n">
         <v>0.7565892370966808</v>
@@ -3083,7 +3083,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>0.6254674411351748</v>
+        <v>0.6254674411351747</v>
       </c>
       <c r="C157" t="n">
         <v>0.60999595167139</v>
@@ -3117,7 +3117,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>0.623010473125761</v>
+        <v>0.6230104731257611</v>
       </c>
       <c r="C159" t="n">
         <v>0.6075374473005521</v>
@@ -3151,7 +3151,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>0.6205672399444511</v>
+        <v>0.620567239944451</v>
       </c>
       <c r="C161" t="n">
         <v>0.6050949867272449</v>
@@ -3168,10 +3168,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>0.6193508462681446</v>
+        <v>0.6193508462681445</v>
       </c>
       <c r="C162" t="n">
-        <v>0.6038798182629653</v>
+        <v>0.6038798182629654</v>
       </c>
       <c r="D162" t="n">
         <v>0.7593697503330823</v>
@@ -3185,7 +3185,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>0.6181379763774155</v>
+        <v>0.6181379763774156</v>
       </c>
       <c r="C163" t="n">
         <v>0.6026687183662471</v>
@@ -3202,7 +3202,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>0.616928663487823</v>
+        <v>0.6169286634878232</v>
       </c>
       <c r="C164" t="n">
         <v>0.6014617093232217</v>
@@ -3219,7 +3219,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>0.6157229421478645</v>
+        <v>0.6157229421478644</v>
       </c>
       <c r="C165" t="n">
         <v>0.600258814709851</v>
@@ -3253,7 +3253,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>0.6133224183228232</v>
+        <v>0.6133224183228231</v>
       </c>
       <c r="C167" t="n">
         <v>0.5978654689049806</v>
@@ -3287,7 +3287,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>0.6109367038544929</v>
+        <v>0.6109367038544931</v>
       </c>
       <c r="C169" t="n">
         <v>0.5954888914691223</v>
@@ -3321,7 +3321,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>0.6085661122564493</v>
+        <v>0.6085661122564494</v>
       </c>
       <c r="C171" t="n">
         <v>0.5931293071450221</v>
@@ -3355,7 +3355,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>0.6062109684155577</v>
+        <v>0.6062109684155575</v>
       </c>
       <c r="C173" t="n">
         <v>0.5907869518945493</v>
@@ -3389,7 +3389,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>0.6038716055409246</v>
+        <v>0.6038716055409244</v>
       </c>
       <c r="C175" t="n">
         <v>0.5884620700324215</v>
@@ -3423,7 +3423,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>0.6015483622515025</v>
+        <v>0.6015483622515027</v>
       </c>
       <c r="C177" t="n">
         <v>0.5861549115006458</v>
@@ -3477,7 +3477,7 @@
         <v>0.5980944681101118</v>
       </c>
       <c r="C180" t="n">
-        <v>0.5827279585812615</v>
+        <v>0.5827279585812616</v>
       </c>
       <c r="D180" t="n">
         <v>0.7667844522968198</v>
@@ -3491,7 +3491,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>0.5969515994636738</v>
+        <v>0.5969515994636737</v>
       </c>
       <c r="C181" t="n">
         <v>0.5815947769714525</v>
@@ -3542,7 +3542,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>0.5935488727441195</v>
+        <v>0.5935488727441196</v>
       </c>
       <c r="C184" t="n">
         <v>0.5782230795838335</v>
@@ -3627,7 +3627,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>0.5879663896315853</v>
+        <v>0.5879663896315854</v>
       </c>
       <c r="C189" t="n">
         <v>0.5726982348777471</v>
@@ -3644,7 +3644,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>0.5868635594039705</v>
+        <v>0.5868635594039706</v>
       </c>
       <c r="C190" t="n">
         <v>0.5716077269185604</v>
@@ -3661,7 +3661,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>0.5857653732578941</v>
+        <v>0.585765373257894</v>
       </c>
       <c r="C191" t="n">
         <v>0.5705221041216015</v>
@@ -3678,10 +3678,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>0.5846718675630945</v>
+        <v>0.5846718675630946</v>
       </c>
       <c r="C192" t="n">
-        <v>0.5694413928752621</v>
+        <v>0.5694413928752622</v>
       </c>
       <c r="D192" t="n">
         <v>0.7728088976423565</v>
@@ -3698,7 +3698,7 @@
         <v>0.5835830777942287</v>
       </c>
       <c r="C193" t="n">
-        <v>0.5683656187873268</v>
+        <v>0.5683656187873269</v>
       </c>
       <c r="D193" t="n">
         <v>0.773677808028732</v>
@@ -3712,7 +3712,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>0.5824990384843507</v>
+        <v>0.5824990384843506</v>
       </c>
       <c r="C194" t="n">
         <v>0.5672948066432919</v>
@@ -3746,7 +3746,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>0.5803453444027922</v>
+        <v>0.5803453444027923</v>
       </c>
       <c r="C196" t="n">
         <v>0.5651681629825918</v>
@@ -3780,7 +3780,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>0.5782110411281197</v>
+        <v>0.5782110411281196</v>
       </c>
       <c r="C198" t="n">
         <v>0.5630616422840001</v>
@@ -3831,7 +3831,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>0.5750464598389705</v>
+        <v>0.5750464598389704</v>
       </c>
       <c r="C201" t="n">
         <v>0.5599399481056646</v>
@@ -3848,7 +3848,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>0.5740015408649844</v>
+        <v>0.5740015408649846</v>
       </c>
       <c r="C202" t="n">
         <v>0.558909613068664</v>
@@ -3882,7 +3882,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>0.5719267630035149</v>
+        <v>0.5719267630035147</v>
       </c>
       <c r="C204" t="n">
         <v>0.5568643843230263</v>
@@ -3902,7 +3902,7 @@
         <v>0.5708969489327069</v>
       </c>
       <c r="C205" t="n">
-        <v>0.5558495189528714</v>
+        <v>0.5558495189528713</v>
       </c>
       <c r="D205" t="n">
         <v>0.7786016335515263</v>
@@ -3916,7 +3916,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>0.5698722124534078</v>
+        <v>0.5698722124534079</v>
       </c>
       <c r="C206" t="n">
         <v>0.5548398365576953</v>
@@ -3967,7 +3967,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>0.5668286526796884</v>
+        <v>0.5668286526796885</v>
       </c>
       <c r="C209" t="n">
         <v>0.5518419939497284</v>
@@ -3984,7 +3984,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>0.5658244038439271</v>
+        <v>0.5658244038439272</v>
       </c>
       <c r="C210" t="n">
         <v>0.5508531442067451</v>
@@ -4038,7 +4038,7 @@
         <v>0.5628426608016608</v>
       </c>
       <c r="C213" t="n">
-        <v>0.54791797876611</v>
+        <v>0.5479179787661101</v>
       </c>
       <c r="D213" t="n">
         <v>0.7803394543242773</v>
@@ -4086,7 +4086,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>0.5599076345967192</v>
+        <v>0.5599076345967191</v>
       </c>
       <c r="C216" t="n">
         <v>0.5450299604023728</v>
@@ -4103,7 +4103,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>0.5589397079137802</v>
+        <v>0.5589397079137801</v>
       </c>
       <c r="C217" t="n">
         <v>0.5440777691468107</v>
@@ -4120,7 +4120,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>0.5579769963175464</v>
+        <v>0.5579769963175465</v>
       </c>
       <c r="C218" t="n">
         <v>0.5431308161430412</v>
@@ -4154,7 +4154,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>0.5560672263043922</v>
+        <v>0.5560672263043921</v>
       </c>
       <c r="C220" t="n">
         <v>0.5412526103256509</v>
@@ -4171,7 +4171,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>0.5551201683625584</v>
+        <v>0.5551201683625583</v>
       </c>
       <c r="C221" t="n">
         <v>0.5403213472082394</v>
@@ -4188,10 +4188,10 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>0.5541783264747026</v>
+        <v>0.5541783264747027</v>
       </c>
       <c r="C222" t="n">
-        <v>0.5393953017518528</v>
+        <v>0.5393953017518527</v>
       </c>
       <c r="D222" t="n">
         <v>0.7829461854834038</v>
@@ -4239,7 +4239,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>0.5513840583048565</v>
+        <v>0.5513840583048564</v>
       </c>
       <c r="C225" t="n">
         <v>0.536648384167332</v>
@@ -4307,7 +4307,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>0.5477310443149435</v>
+        <v>0.5477310443149436</v>
       </c>
       <c r="C229" t="n">
         <v>0.5330582488098071</v>
@@ -4341,7 +4341,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>0.5459355019880511</v>
+        <v>0.5459355019880512</v>
       </c>
       <c r="C231" t="n">
         <v>0.53129396478532</v>
@@ -4375,7 +4375,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>0.5441604577348023</v>
+        <v>0.5441604577348021</v>
       </c>
       <c r="C233" t="n">
         <v>0.5295500209543573</v>
@@ -4409,7 +4409,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>0.542405778753933</v>
+        <v>0.5424057787539331</v>
       </c>
       <c r="C235" t="n">
         <v>0.5278262600459452</v>
@@ -4429,7 +4429,7 @@
         <v>0.5415360297094302</v>
       </c>
       <c r="C236" t="n">
-        <v>0.526971894739487</v>
+        <v>0.5269718947394871</v>
       </c>
       <c r="D236" t="n">
         <v>0.7848577883334299</v>
@@ -4443,7 +4443,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>0.5406713139253964</v>
+        <v>0.5406713139253965</v>
       </c>
       <c r="C237" t="n">
         <v>0.5261225091313445</v>
@@ -4460,7 +4460,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>0.5398116097819879</v>
+        <v>0.5398116097819881</v>
       </c>
       <c r="C238" t="n">
         <v>0.5252780792780711</v>
@@ -4528,10 +4528,10 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>0.5364224413376837</v>
+        <v>0.5364224413376836</v>
       </c>
       <c r="C242" t="n">
-        <v>0.5219494080548023</v>
+        <v>0.5219494080548024</v>
       </c>
       <c r="D242" t="n">
         <v>0.7845102241788797</v>
@@ -4565,7 +4565,7 @@
         <v>0.5347572909028324</v>
       </c>
       <c r="C244" t="n">
-        <v>0.5203141216689096</v>
+        <v>0.5203141216689097</v>
       </c>
       <c r="D244" t="n">
         <v>0.7846840062561548</v>
@@ -4579,7 +4579,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>0.5339319788959017</v>
+        <v>0.5339319788959016</v>
       </c>
       <c r="C245" t="n">
         <v>0.5195036403965507</v>
@@ -4596,7 +4596,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>0.5331114704262536</v>
+        <v>0.5331114704262537</v>
       </c>
       <c r="C246" t="n">
         <v>0.5186978935382757</v>
@@ -4613,7 +4613,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>0.5322957355193647</v>
+        <v>0.5322957355193649</v>
       </c>
       <c r="C247" t="n">
         <v>0.5178968500856214</v>
@@ -4630,7 +4630,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>0.531484743418688</v>
+        <v>0.5314847434186881</v>
       </c>
       <c r="C248" t="n">
         <v>0.51710047837472</v>
@@ -4647,7 +4647,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>0.5306784626155594</v>
+        <v>0.5306784626155593</v>
       </c>
       <c r="C249" t="n">
         <v>0.5163087461126679</v>
@@ -4664,7 +4664,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>0.529876860879139</v>
+        <v>0.5298768608791389</v>
       </c>
       <c r="C250" t="n">
         <v>0.5155216204038949</v>
@@ -4684,7 +4684,7 @@
         <v>0.5290799052863431</v>
       </c>
       <c r="C251" t="n">
-        <v>0.5147390677764928</v>
+        <v>0.5147390677764929</v>
       </c>
       <c r="D251" t="n">
         <v>0.7847998609743382</v>
@@ -4715,7 +4715,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>0.5274997975572411</v>
+        <v>0.527499797557241</v>
       </c>
       <c r="C253" t="n">
         <v>0.5131875451538872</v>
@@ -4752,7 +4752,7 @@
         <v>0.5259378633313604</v>
       </c>
       <c r="C255" t="n">
-        <v>0.5116538999373922</v>
+        <v>0.5116538999373923</v>
       </c>
       <c r="D255" t="n">
         <v>0.7852053524879801</v>
@@ -4783,7 +4783,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>0.5243938173347176</v>
+        <v>0.5243938173347175</v>
       </c>
       <c r="C257" t="n">
         <v>0.5101378462638073</v>
@@ -4800,7 +4800,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>0.5236284109945626</v>
+        <v>0.5236284109945625</v>
       </c>
       <c r="C258" t="n">
         <v>0.5093863250582743</v>
@@ -4817,10 +4817,10 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>0.5228673660481393</v>
+        <v>0.5228673660481394</v>
       </c>
       <c r="C259" t="n">
-        <v>0.5086390915293538</v>
+        <v>0.5086390915293537</v>
       </c>
       <c r="D259" t="n">
         <v>0.7853212072061635</v>
@@ -4834,7 +4834,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>0.5221106446672145</v>
+        <v>0.5221106446672146</v>
       </c>
       <c r="C260" t="n">
         <v>0.5078961081793073</v>
@@ -4851,7 +4851,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>0.5213582086213228</v>
+        <v>0.5213582086213226</v>
       </c>
       <c r="C261" t="n">
         <v>0.5071573371877819</v>
@@ -4868,7 +4868,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>0.5206100193050802</v>
+        <v>0.5206100193050803</v>
       </c>
       <c r="C262" t="n">
         <v>0.5064227404355903</v>
@@ -4919,10 +4919,10 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>0.5183905406182253</v>
+        <v>0.5183905406182252</v>
       </c>
       <c r="C265" t="n">
-        <v>0.5042436104290218</v>
+        <v>0.5042436104290217</v>
       </c>
       <c r="D265" t="n">
         <v>0.7855529166425302</v>
@@ -4936,7 +4936,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>0.517658945600085</v>
+        <v>0.5176589456000851</v>
       </c>
       <c r="C266" t="n">
         <v>0.5035253242757264</v>
@@ -4953,7 +4953,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>0.5169313995860829</v>
+        <v>0.5169313995860828</v>
       </c>
       <c r="C267" t="n">
         <v>0.5028110180875359</v>
@@ -4970,7 +4970,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>0.516207862269749</v>
+        <v>0.5162078622697491</v>
       </c>
       <c r="C268" t="n">
         <v>0.5021006524287601</v>
@@ -4987,7 +4987,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>0.5154882931478957</v>
+        <v>0.5154882931478958</v>
       </c>
       <c r="C269" t="n">
         <v>0.5013941877195668</v>
@@ -5041,7 +5041,7 @@
         <v>0.5133529874537407</v>
       </c>
       <c r="C272" t="n">
-        <v>0.49929780175068</v>
+        <v>0.4992978017506799</v>
       </c>
       <c r="D272" t="n">
         <v>0.7871169553380062</v>
@@ -5109,7 +5109,7 @@
         <v>0.5105589857045062</v>
       </c>
       <c r="C276" t="n">
-        <v>0.4965548154893054</v>
+        <v>0.4965548154893055</v>
       </c>
       <c r="D276" t="n">
         <v>0.7882175751607484</v>
@@ -5123,7 +5123,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>0.5098696878723359</v>
+        <v>0.509869687872336</v>
       </c>
       <c r="C277" t="n">
         <v>0.4958781226542313</v>
@@ -5157,7 +5157,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="n">
-        <v>0.5085018463799914</v>
+        <v>0.5085018463799913</v>
       </c>
       <c r="C279" t="n">
         <v>0.4945353212478823</v>
@@ -5276,7 +5276,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>0.5038229958197038</v>
+        <v>0.5038229958197037</v>
       </c>
       <c r="C286" t="n">
         <v>0.4899424661337802</v>
@@ -5293,7 +5293,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>0.5031678321100584</v>
+        <v>0.5031678321100583</v>
       </c>
       <c r="C287" t="n">
         <v>0.4892993968440784</v>
@@ -5310,7 +5310,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>0.5025158572900775</v>
+        <v>0.5025158572900774</v>
       </c>
       <c r="C288" t="n">
         <v>0.4886594729673145</v>
@@ -5330,7 +5330,7 @@
         <v>0.5018670310586403</v>
       </c>
       <c r="C289" t="n">
-        <v>0.4880226556108351</v>
+        <v>0.488022655610835</v>
       </c>
       <c r="D289" t="n">
         <v>0.7914035799107919</v>
@@ -5429,10 +5429,10 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>0.4980379601982814</v>
+        <v>0.4980379601982813</v>
       </c>
       <c r="C295" t="n">
-        <v>0.4842648334494409</v>
+        <v>0.4842648334494408</v>
       </c>
       <c r="D295" t="n">
         <v>0.7928517638880843</v>
@@ -5480,7 +5480,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>0.4961627253002939</v>
+        <v>0.4961627253002938</v>
       </c>
       <c r="C298" t="n">
         <v>0.4824247686493148</v>
@@ -5497,7 +5497,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>0.495543211377858</v>
+        <v>0.4955432113778579</v>
       </c>
       <c r="C299" t="n">
         <v>0.4818169200019529</v>
@@ -5531,7 +5531,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>0.4943123024745381</v>
+        <v>0.4943123024745382</v>
       </c>
       <c r="C301" t="n">
         <v>0.480609262623188</v>
@@ -5548,7 +5548,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>0.4937008325597444</v>
+        <v>0.4937008325597445</v>
       </c>
       <c r="C302" t="n">
         <v>0.4800093816181827</v>
@@ -5667,10 +5667,10 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>0.4894914973293013</v>
+        <v>0.4894914973293011</v>
       </c>
       <c r="C309" t="n">
-        <v>0.4758806012148538</v>
+        <v>0.4758806012148539</v>
       </c>
       <c r="D309" t="n">
         <v>0.7964432601517697</v>
@@ -5684,7 +5684,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>0.488899869596576</v>
+        <v>0.4888998695965759</v>
       </c>
       <c r="C310" t="n">
         <v>0.4753004151720192</v>
@@ -5701,7 +5701,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="n">
-        <v>0.4883105630144166</v>
+        <v>0.4883105630144164</v>
       </c>
       <c r="C311" t="n">
         <v>0.4747225373438704</v>
@@ -5718,10 +5718,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>0.487723543259243</v>
+        <v>0.4877235432592429</v>
       </c>
       <c r="C312" t="n">
-        <v>0.4741469345593252</v>
+        <v>0.4741469345593253</v>
       </c>
       <c r="D312" t="n">
         <v>0.7970225337426867</v>
@@ -5803,7 +5803,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>0.4848215679884449</v>
+        <v>0.4848215679884448</v>
       </c>
       <c r="C317" t="n">
         <v>0.4713019063177965</v>
@@ -5871,7 +5871,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>0.482537768520892</v>
+        <v>0.4825377685208921</v>
       </c>
       <c r="C321" t="n">
         <v>0.4690635623822528</v>
@@ -5922,7 +5922,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>0.4808456251473592</v>
+        <v>0.4808456251473591</v>
       </c>
       <c r="C324" t="n">
         <v>0.4674054924965006</v>
@@ -5939,7 +5939,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>0.4802853578864829</v>
+        <v>0.4802853578864828</v>
       </c>
       <c r="C325" t="n">
         <v>0.4668565844855453</v>
@@ -5959,7 +5959,7 @@
         <v>0.479726931026356</v>
       </c>
       <c r="C326" t="n">
-        <v>0.4663095190286781</v>
+        <v>0.4663095190286782</v>
       </c>
       <c r="D326" t="n">
         <v>0.7992237733881712</v>
@@ -5993,7 +5993,7 @@
         <v>0.4786154811297226</v>
       </c>
       <c r="C328" t="n">
-        <v>0.4652208017088888</v>
+        <v>0.4652208017088889</v>
       </c>
       <c r="D328" t="n">
         <v>0.7992237733881712</v>
@@ -6024,7 +6024,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>0.4775110439666705</v>
+        <v>0.4775110439666707</v>
       </c>
       <c r="C330" t="n">
         <v>0.4641391154494459</v>
@@ -6041,10 +6041,10 @@
         <v>330</v>
       </c>
       <c r="B331" t="n">
-        <v>0.4769613842433184</v>
+        <v>0.4769613842433183</v>
       </c>
       <c r="C331" t="n">
-        <v>0.4636008399566727</v>
+        <v>0.4636008399566726</v>
       </c>
       <c r="D331" t="n">
         <v>0.7993396281063546</v>
@@ -6126,7 +6126,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="n">
-        <v>0.4742375717964629</v>
+        <v>0.4742375717964628</v>
       </c>
       <c r="C336" t="n">
         <v>0.4609340648118986</v>
@@ -6180,7 +6180,7 @@
         <v>0.4726219126492958</v>
       </c>
       <c r="C339" t="n">
-        <v>0.4593527444118945</v>
+        <v>0.4593527444118944</v>
       </c>
       <c r="D339" t="n">
         <v>0.8002085384927301</v>
@@ -6194,7 +6194,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>0.4720863089376969</v>
+        <v>0.472086308937697</v>
       </c>
       <c r="C340" t="n">
         <v>0.4588286099428788</v>
@@ -6282,7 +6282,7 @@
         <v>0.4694292936830438</v>
       </c>
       <c r="C345" t="n">
-        <v>0.45622913720513</v>
+        <v>0.4562291372051299</v>
       </c>
       <c r="D345" t="n">
         <v>0.8010195215200139</v>
@@ -6381,7 +6381,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="n">
-        <v>0.4662839554957717</v>
+        <v>0.4662839554957718</v>
       </c>
       <c r="C351" t="n">
         <v>0.4531533424703916</v>
@@ -6435,7 +6435,7 @@
         <v>0.464727486489754</v>
       </c>
       <c r="C354" t="n">
-        <v>0.4516318712796603</v>
+        <v>0.4516318712796604</v>
       </c>
       <c r="D354" t="n">
         <v>0.8028731970109483</v>
@@ -6534,7 +6534,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>0.4616440878593974</v>
+        <v>0.4616440878593973</v>
       </c>
       <c r="C360" t="n">
         <v>0.4486189618591742</v>
@@ -6571,7 +6571,7 @@
         <v>0.4606244527462627</v>
       </c>
       <c r="C362" t="n">
-        <v>0.4476229764447427</v>
+        <v>0.4476229764447428</v>
       </c>
       <c r="D362" t="n">
         <v>0.8047268725018827</v>
@@ -6653,10 +6653,10 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>0.4580917828704092</v>
+        <v>0.4580917828704091</v>
       </c>
       <c r="C367" t="n">
-        <v>0.4451497800348746</v>
+        <v>0.4451497800348747</v>
       </c>
       <c r="D367" t="n">
         <v>0.8053061460927996</v>
@@ -6670,7 +6670,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="n">
-        <v>0.4575879182648005</v>
+        <v>0.4575879182648004</v>
       </c>
       <c r="C368" t="n">
         <v>0.4446578710812652</v>
@@ -6707,7 +6707,7 @@
         <v>0.4565827181040532</v>
       </c>
       <c r="C370" t="n">
-        <v>0.4436766440291177</v>
+        <v>0.4436766440291178</v>
       </c>
       <c r="D370" t="n">
         <v>0.8062329838382668</v>
@@ -6721,7 +6721,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>0.4560813485252482</v>
+        <v>0.4560813485252481</v>
       </c>
       <c r="C371" t="n">
         <v>0.4431872920657369</v>
@@ -6789,10 +6789,10 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>0.4540836872473697</v>
+        <v>0.4540836872473696</v>
       </c>
       <c r="C375" t="n">
-        <v>0.4412379096662294</v>
+        <v>0.4412379096662295</v>
       </c>
       <c r="D375" t="n">
         <v>0.8073915310201008</v>
@@ -6942,7 +6942,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>0.4496303986950999</v>
+        <v>0.4496303986951</v>
       </c>
       <c r="C384" t="n">
         <v>0.4368944726483588</v>
@@ -6962,7 +6962,7 @@
         <v>0.4491387841371822</v>
       </c>
       <c r="C385" t="n">
-        <v>0.4364151680593447</v>
+        <v>0.4364151680593448</v>
       </c>
       <c r="D385" t="n">
         <v>0.8094189885883103</v>
@@ -6996,7 +6996,7 @@
         <v>0.4481573032527319</v>
       </c>
       <c r="C387" t="n">
-        <v>0.435458369075431</v>
+        <v>0.4354583690754311</v>
       </c>
       <c r="D387" t="n">
         <v>0.8097665527428605</v>
@@ -7010,7 +7010,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>0.4476674100346733</v>
+        <v>0.4476674100346734</v>
       </c>
       <c r="C388" t="n">
         <v>0.4349808476450074</v>
@@ -7027,7 +7027,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>0.4471780640186783</v>
+        <v>0.4471780640186784</v>
       </c>
       <c r="C389" t="n">
         <v>0.434503893868076</v>
@@ -7044,7 +7044,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="n">
-        <v>0.4466892522261117</v>
+        <v>0.4466892522261118</v>
       </c>
       <c r="C390" t="n">
         <v>0.4340274946781492</v>
@@ -7061,7 +7061,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="n">
-        <v>0.4462009618612333</v>
+        <v>0.4462009618612332</v>
       </c>
       <c r="C391" t="n">
         <v>0.4335516371857351</v>
@@ -7098,7 +7098,7 @@
         <v>0.4452258951331414</v>
       </c>
       <c r="C393" t="n">
-        <v>0.4326014966089867</v>
+        <v>0.4326014966089866</v>
       </c>
       <c r="D393" t="n">
         <v>0.8111568093610613</v>
@@ -7129,7 +7129,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="n">
-        <v>0.444252765045088</v>
+        <v>0.4442527650450879</v>
       </c>
       <c r="C395" t="n">
         <v>0.4316533724895993</v>
@@ -7146,7 +7146,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="n">
-        <v>0.4437668961343883</v>
+        <v>0.4437668961343884</v>
       </c>
       <c r="C396" t="n">
         <v>0.4311800362044357</v>
@@ -7180,7 +7180,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="n">
-        <v>0.4427964918640077</v>
+        <v>0.4427964918640076</v>
       </c>
       <c r="C398" t="n">
         <v>0.4302347558467679</v>
@@ -7282,10 +7282,10 @@
         <v>403</v>
       </c>
       <c r="B404" t="n">
-        <v>0.4398951348300476</v>
+        <v>0.4398951348300477</v>
       </c>
       <c r="C404" t="n">
-        <v>0.4274092301085986</v>
+        <v>0.4274092301085987</v>
       </c>
       <c r="D404" t="n">
         <v>0.8141111046747379</v>
@@ -7299,7 +7299,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="n">
-        <v>0.4394128983543938</v>
+        <v>0.4394128983543939</v>
       </c>
       <c r="C405" t="n">
         <v>0.4269396976890034</v>
@@ -7353,7 +7353,7 @@
         <v>0.4379682487191526</v>
       </c>
       <c r="C408" t="n">
-        <v>0.4255332694596036</v>
+        <v>0.4255332694596037</v>
       </c>
       <c r="D408" t="n">
         <v>0.8151537971383884</v>
@@ -7367,7 +7367,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="n">
-        <v>0.4374873521216051</v>
+        <v>0.437487352121605</v>
       </c>
       <c r="C409" t="n">
         <v>0.4250651492104603</v>
@@ -7384,7 +7384,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="n">
-        <v>0.4370067658760906</v>
+        <v>0.4370067658760905</v>
       </c>
       <c r="C410" t="n">
         <v>0.4245973569817418</v>
@@ -7418,7 +7418,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="n">
-        <v>0.4360464863659382</v>
+        <v>0.4360464863659383</v>
       </c>
       <c r="C412" t="n">
         <v>0.4236627178463689</v>
@@ -7469,7 +7469,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="n">
-        <v>0.4346081605004508</v>
+        <v>0.4346081605004509</v>
       </c>
       <c r="C415" t="n">
         <v>0.4222629808684251</v>
@@ -7486,7 +7486,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="n">
-        <v>0.4341292406818053</v>
+        <v>0.4341292406818054</v>
       </c>
       <c r="C416" t="n">
         <v>0.4217969575501212</v>
@@ -7608,7 +7608,7 @@
         <v>0.4307832304087644</v>
       </c>
       <c r="C423" t="n">
-        <v>0.418541674543563</v>
+        <v>0.4185416745435631</v>
       </c>
       <c r="D423" t="n">
         <v>0.8189770028384405</v>
@@ -7673,10 +7673,10 @@
         <v>426</v>
       </c>
       <c r="B427" t="n">
-        <v>0.4288755630747396</v>
+        <v>0.4288755630747397</v>
       </c>
       <c r="C427" t="n">
-        <v>0.4166861909933267</v>
+        <v>0.4166861909933266</v>
       </c>
       <c r="D427" t="n">
         <v>0.8199617679429995</v>
@@ -7707,7 +7707,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="n">
-        <v>0.4279227136547373</v>
+        <v>0.4279227136547374</v>
       </c>
       <c r="C429" t="n">
         <v>0.4157595215744141</v>
@@ -7792,7 +7792,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="n">
-        <v>0.4255430048575849</v>
+        <v>0.425543004857585</v>
       </c>
       <c r="C434" t="n">
         <v>0.413445508764701</v>
@@ -7809,10 +7809,10 @@
         <v>434</v>
       </c>
       <c r="B435" t="n">
-        <v>0.4250674230254444</v>
+        <v>0.4250674230254443</v>
       </c>
       <c r="C435" t="n">
-        <v>0.4129831069478938</v>
+        <v>0.4129831069478937</v>
       </c>
       <c r="D435" t="n">
         <v>0.8222209349475758</v>
@@ -7863,7 +7863,7 @@
         <v>0.4236412814743751</v>
       </c>
       <c r="C438" t="n">
-        <v>0.4115965840918896</v>
+        <v>0.4115965840918897</v>
       </c>
       <c r="D438" t="n">
         <v>0.8237270462839599</v>
@@ -7877,7 +7877,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="n">
-        <v>0.4231660817413997</v>
+        <v>0.4231660817413998</v>
       </c>
       <c r="C439" t="n">
         <v>0.4111346162639984</v>
@@ -7931,7 +7931,7 @@
         <v>0.4217409417362248</v>
       </c>
       <c r="C442" t="n">
-        <v>0.4097492467513075</v>
+        <v>0.4097492467513076</v>
       </c>
       <c r="D442" t="n">
         <v>0.8249435208248856</v>
@@ -8149,7 +8149,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="n">
-        <v>0.4155701074819935</v>
+        <v>0.4155701074819934</v>
       </c>
       <c r="C455" t="n">
         <v>0.4037519573026969</v>
@@ -8254,7 +8254,7 @@
         <v>0.4127226328608435</v>
       </c>
       <c r="C461" t="n">
-        <v>0.4009851809225735</v>
+        <v>0.4009851809225734</v>
       </c>
       <c r="D461" t="n">
         <v>0.8324740775068065</v>
@@ -8271,7 +8271,7 @@
         <v>0.4122479918550381</v>
       </c>
       <c r="C462" t="n">
-        <v>0.4005240233286948</v>
+        <v>0.4005240233286949</v>
       </c>
       <c r="D462" t="n">
         <v>0.8326478595840816</v>
@@ -8373,7 +8373,7 @@
         <v>0.4093994464259609</v>
       </c>
       <c r="C468" t="n">
-        <v>0.3977565689526606</v>
+        <v>0.3977565689526607</v>
       </c>
       <c r="D468" t="n">
         <v>0.8341539709204657</v>
@@ -8438,7 +8438,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="n">
-        <v>0.4074995155692927</v>
+        <v>0.4074995155692926</v>
       </c>
       <c r="C472" t="n">
         <v>0.3959108712091537</v>
@@ -8540,10 +8540,10 @@
         <v>477</v>
       </c>
       <c r="B478" t="n">
-        <v>0.4046478212399714</v>
+        <v>0.4046478212399713</v>
       </c>
       <c r="C478" t="n">
-        <v>0.393140765742741</v>
+        <v>0.3931407657427409</v>
       </c>
       <c r="D478" t="n">
         <v>0.8375137577477842</v>
@@ -8557,7 +8557,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="n">
-        <v>0.404172298349061</v>
+        <v>0.4041722983490611</v>
       </c>
       <c r="C479" t="n">
         <v>0.3926788673617156</v>
@@ -8642,7 +8642,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="n">
-        <v>0.401793532005349</v>
+        <v>0.4017935320053491</v>
       </c>
       <c r="C484" t="n">
         <v>0.3903683293540565</v>
@@ -8662,7 +8662,7 @@
         <v>0.4013175363542317</v>
       </c>
       <c r="C485" t="n">
-        <v>0.3899059996779667</v>
+        <v>0.3899059996779668</v>
       </c>
       <c r="D485" t="n">
         <v>0.8395991426750854</v>
@@ -8679,7 +8679,7 @@
         <v>0.4008414563445857</v>
       </c>
       <c r="C486" t="n">
-        <v>0.3894435921265132</v>
+        <v>0.3894435921265133</v>
       </c>
       <c r="D486" t="n">
         <v>0.8397729247523605</v>
@@ -8710,7 +8710,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="n">
-        <v>0.3998890379826707</v>
+        <v>0.3998890379826706</v>
       </c>
       <c r="C488" t="n">
         <v>0.3885185376325952</v>
@@ -8744,7 +8744,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="n">
-        <v>0.3989362673233946</v>
+        <v>0.3989362673233947</v>
       </c>
       <c r="C490" t="n">
         <v>0.3875931552699386</v>
@@ -8846,7 +8846,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="n">
-        <v>0.3960757681356633</v>
+        <v>0.3960757681356632</v>
       </c>
       <c r="C496" t="n">
         <v>0.3848149571813552</v>
@@ -8880,7 +8880,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="n">
-        <v>0.3951215223869283</v>
+        <v>0.3951215223869282</v>
       </c>
       <c r="C498" t="n">
         <v>0.3838881869592569</v>
@@ -8897,7 +8897,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="n">
-        <v>0.3946442579399596</v>
+        <v>0.3946442579399595</v>
       </c>
       <c r="C499" t="n">
         <v>0.3834246674927245</v>
@@ -9118,7 +9118,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="n">
-        <v>0.3884313010944027</v>
+        <v>0.3884313010944026</v>
       </c>
       <c r="C512" t="n">
         <v>0.3773907598768835</v>
@@ -9135,7 +9135,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="n">
-        <v>0.3879527451525569</v>
+        <v>0.387952745152557</v>
       </c>
       <c r="C513" t="n">
         <v>0.3769259993130376</v>
@@ -9220,7 +9220,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="n">
-        <v>0.3855586991655609</v>
+        <v>0.3855586991655608</v>
       </c>
       <c r="C518" t="n">
         <v>0.3746009613276968</v>
@@ -9237,7 +9237,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="n">
-        <v>0.3850796471756108</v>
+        <v>0.3850796471756109</v>
       </c>
       <c r="C519" t="n">
         <v>0.3741357158095961</v>
@@ -9257,7 +9257,7 @@
         <v>0.3846005181835415</v>
       </c>
       <c r="C520" t="n">
-        <v>0.3736703944467817</v>
+        <v>0.3736703944467816</v>
       </c>
       <c r="D520" t="n">
         <v>0.8493309390024909</v>
@@ -9271,7 +9271,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="n">
-        <v>0.3841213140616932</v>
+        <v>0.3841213140616931</v>
       </c>
       <c r="C521" t="n">
         <v>0.3732049989045939</v>
@@ -9288,7 +9288,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>0.3836420367764406</v>
+        <v>0.3836420367764405</v>
       </c>
       <c r="C522" t="n">
         <v>0.37273953093878</v>
@@ -9325,7 +9325,7 @@
         <v>0.3826832710503058</v>
       </c>
       <c r="C524" t="n">
-        <v>0.3718083852099863</v>
+        <v>0.3718083852099864</v>
       </c>
       <c r="D524" t="n">
         <v>0.8505474135434166</v>
@@ -9356,7 +9356,7 @@
         <v>525</v>
       </c>
       <c r="B526" t="n">
-        <v>0.3817242386095804</v>
+        <v>0.3817242386095803</v>
       </c>
       <c r="C526" t="n">
         <v>0.3708769731059129</v>
@@ -9424,10 +9424,10 @@
         <v>529</v>
       </c>
       <c r="B530" t="n">
-        <v>0.3798054514491874</v>
+        <v>0.3798054514491875</v>
       </c>
       <c r="C530" t="n">
-        <v>0.3690134202995794</v>
+        <v>0.3690134202995793</v>
       </c>
       <c r="D530" t="n">
         <v>0.8516480333661588</v>
@@ -9529,7 +9529,7 @@
         <v>0.376925795699887</v>
       </c>
       <c r="C536" t="n">
-        <v>0.366216571160506</v>
+        <v>0.3662165711605061</v>
       </c>
       <c r="D536" t="n">
         <v>0.8527486531889011</v>
@@ -9546,7 +9546,7 @@
         <v>0.3764457201530933</v>
       </c>
       <c r="C537" t="n">
-        <v>0.365750288199211</v>
+        <v>0.3657502881992111</v>
       </c>
       <c r="D537" t="n">
         <v>0.8527486531889011</v>
@@ -9614,7 +9614,7 @@
         <v>0.3745251623931989</v>
       </c>
       <c r="C541" t="n">
-        <v>0.3638848665609205</v>
+        <v>0.3638848665609206</v>
       </c>
       <c r="D541" t="n">
         <v>0.854312691884377</v>
@@ -9628,7 +9628,7 @@
         <v>541</v>
       </c>
       <c r="B542" t="n">
-        <v>0.3740449773151358</v>
+        <v>0.3740449773151357</v>
       </c>
       <c r="C542" t="n">
         <v>0.3634184555524779</v>
@@ -9747,7 +9747,7 @@
         <v>548</v>
       </c>
       <c r="B549" t="n">
-        <v>0.3706836106621647</v>
+        <v>0.3706836106621648</v>
       </c>
       <c r="C549" t="n">
         <v>0.3601533629829882</v>
@@ -9781,7 +9781,7 @@
         <v>550</v>
       </c>
       <c r="B551" t="n">
-        <v>0.369723323953733</v>
+        <v>0.3697233239537329</v>
       </c>
       <c r="C551" t="n">
         <v>0.3592205275630617</v>
@@ -9801,7 +9801,7 @@
         <v>0.3692432201099112</v>
       </c>
       <c r="C552" t="n">
-        <v>0.3587541385207154</v>
+        <v>0.3587541385207155</v>
       </c>
       <c r="D552" t="n">
         <v>0.8570352777616869</v>
@@ -9832,7 +9832,7 @@
         <v>553</v>
       </c>
       <c r="B554" t="n">
-        <v>0.3682831148395563</v>
+        <v>0.3682831148395562</v>
       </c>
       <c r="C554" t="n">
         <v>0.3578214395402773</v>
@@ -10070,7 +10070,7 @@
         <v>567</v>
       </c>
       <c r="B568" t="n">
-        <v>0.3615693926683112</v>
+        <v>0.3615693926683113</v>
       </c>
       <c r="C568" t="n">
         <v>0.3512984754442918</v>
@@ -10090,7 +10090,7 @@
         <v>0.3610905376849044</v>
       </c>
       <c r="C569" t="n">
-        <v>0.350833158368453</v>
+        <v>0.3508331583684529</v>
       </c>
       <c r="D569" t="n">
         <v>0.8613219023344726</v>
@@ -10121,7 +10121,7 @@
         <v>570</v>
       </c>
       <c r="B571" t="n">
-        <v>0.3601332022652771</v>
+        <v>0.360133202265277</v>
       </c>
       <c r="C571" t="n">
         <v>0.349902857529084</v>
@@ -10192,7 +10192,7 @@
         <v>0.3582201960662243</v>
       </c>
       <c r="C575" t="n">
-        <v>0.3480437451170222</v>
+        <v>0.3480437451170223</v>
       </c>
       <c r="D575" t="n">
         <v>0.8631176504663153</v>
@@ -10206,7 +10206,7 @@
         <v>575</v>
       </c>
       <c r="B576" t="n">
-        <v>0.357742326593361</v>
+        <v>0.3577423265933611</v>
       </c>
       <c r="C576" t="n">
         <v>0.3475793103643724</v>
@@ -10291,7 +10291,7 @@
         <v>580</v>
       </c>
       <c r="B581" t="n">
-        <v>0.3553555811686346</v>
+        <v>0.3553555811686345</v>
       </c>
       <c r="C581" t="n">
         <v>0.3452594872355484</v>
@@ -10308,7 +10308,7 @@
         <v>581</v>
       </c>
       <c r="B582" t="n">
-        <v>0.3548787966307515</v>
+        <v>0.3548787966307514</v>
       </c>
       <c r="C582" t="n">
         <v>0.3447960342269693</v>
@@ -10376,7 +10376,7 @@
         <v>585</v>
       </c>
       <c r="B586" t="n">
-        <v>0.352973754095754</v>
+        <v>0.3529737540957539</v>
       </c>
       <c r="C586" t="n">
         <v>0.342944128620411</v>
@@ -10393,7 +10393,7 @@
         <v>586</v>
       </c>
       <c r="B587" t="n">
-        <v>0.3524980499062164</v>
+        <v>0.3524980499062165</v>
       </c>
       <c r="C587" t="n">
         <v>0.3424816594491067</v>
@@ -10410,7 +10410,7 @@
         <v>587</v>
       </c>
       <c r="B588" t="n">
-        <v>0.3520225814159223</v>
+        <v>0.3520225814159222</v>
       </c>
       <c r="C588" t="n">
         <v>0.3420194055249384</v>
@@ -10461,7 +10461,7 @@
         <v>590</v>
       </c>
       <c r="B591" t="n">
-        <v>0.3505976563482526</v>
+        <v>0.3505976563482527</v>
       </c>
       <c r="C591" t="n">
         <v>0.340633997616075</v>
@@ -10478,7 +10478,7 @@
         <v>591</v>
       </c>
       <c r="B592" t="n">
-        <v>0.3501231969784066</v>
+        <v>0.3501231969784065</v>
       </c>
       <c r="C592" t="n">
         <v>0.3401726671794265</v>
@@ -10580,7 +10580,7 @@
         <v>597</v>
       </c>
       <c r="B598" t="n">
-        <v>0.3472823246306815</v>
+        <v>0.3472823246306814</v>
       </c>
       <c r="C598" t="n">
         <v>0.3374100855808788</v>
@@ -10614,7 +10614,7 @@
         <v>599</v>
       </c>
       <c r="B600" t="n">
-        <v>0.3463377706579303</v>
+        <v>0.3463377706579304</v>
       </c>
       <c r="C600" t="n">
         <v>0.33649143553863</v>
@@ -10665,10 +10665,10 @@
         <v>602</v>
       </c>
       <c r="B603" t="n">
-        <v>0.3449233793145502</v>
+        <v>0.3449233793145503</v>
       </c>
       <c r="C603" t="n">
-        <v>0.3351157089164163</v>
+        <v>0.3351157089164164</v>
       </c>
       <c r="D603" t="n">
         <v>0.8705902797891444</v>
@@ -10682,7 +10682,7 @@
         <v>603</v>
       </c>
       <c r="B604" t="n">
-        <v>0.3444525932542742</v>
+        <v>0.3444525932542743</v>
       </c>
       <c r="C604" t="n">
         <v>0.3346577586450816</v>
@@ -10719,7 +10719,7 @@
         <v>0.3435120784403621</v>
       </c>
       <c r="C606" t="n">
-        <v>0.3337428345472337</v>
+        <v>0.3337428345472338</v>
       </c>
       <c r="D606" t="n">
         <v>0.871053698661878</v>
@@ -10804,7 +10804,7 @@
         <v>0.3411672750905518</v>
       </c>
       <c r="C611" t="n">
-        <v>0.3314615195753922</v>
+        <v>0.3314615195753923</v>
       </c>
       <c r="D611" t="n">
         <v>0.8720384637664369</v>
@@ -10818,7 +10818,7 @@
         <v>611</v>
       </c>
       <c r="B612" t="n">
-        <v>0.3406994799198832</v>
+        <v>0.3406994799198833</v>
       </c>
       <c r="C612" t="n">
         <v>0.3310063355286691</v>
@@ -10852,10 +10852,10 @@
         <v>613</v>
       </c>
       <c r="B614" t="n">
-        <v>0.3397651088223204</v>
+        <v>0.3397651088223202</v>
       </c>
       <c r="C614" t="n">
-        <v>0.3300970973539725</v>
+        <v>0.3300970973539726</v>
       </c>
       <c r="D614" t="n">
         <v>0.8724439552800788</v>
@@ -10920,7 +10920,7 @@
         <v>617</v>
       </c>
       <c r="B618" t="n">
-        <v>0.337901430198422</v>
+        <v>0.3379014301984221</v>
       </c>
       <c r="C618" t="n">
         <v>0.3282833177990354</v>
@@ -10937,7 +10937,7 @@
         <v>618</v>
       </c>
       <c r="B619" t="n">
-        <v>0.3374366040683624</v>
+        <v>0.3374366040683623</v>
       </c>
       <c r="C619" t="n">
         <v>0.3278308880842171</v>
@@ -10974,7 +10974,7 @@
         <v>0.3365083099784288</v>
       </c>
       <c r="C621" t="n">
-        <v>0.3269272905223149</v>
+        <v>0.3269272905223148</v>
       </c>
       <c r="D621" t="n">
         <v>0.8736025024619127</v>
@@ -11022,7 +11022,7 @@
         <v>623</v>
       </c>
       <c r="B624" t="n">
-        <v>0.3351193616219925</v>
+        <v>0.3351193616219924</v>
       </c>
       <c r="C624" t="n">
         <v>0.3255751414360678</v>
@@ -11039,7 +11039,7 @@
         <v>624</v>
       </c>
       <c r="B625" t="n">
-        <v>0.3346573359791162</v>
+        <v>0.3346573359791161</v>
       </c>
       <c r="C625" t="n">
         <v>0.3251253154965025</v>
@@ -11076,7 +11076,7 @@
         <v>0.33373475859207</v>
       </c>
       <c r="C627" t="n">
-        <v>0.324227035605542</v>
+        <v>0.3242270356055419</v>
       </c>
       <c r="D627" t="n">
         <v>0.8751665411573887</v>
@@ -11127,7 +11127,7 @@
         <v>0.3323546714441649</v>
       </c>
       <c r="C630" t="n">
-        <v>0.322883135468025</v>
+        <v>0.3228831354680251</v>
       </c>
       <c r="D630" t="n">
         <v>0.875861669466489</v>
@@ -11141,10 +11141,10 @@
         <v>630</v>
       </c>
       <c r="B631" t="n">
-        <v>0.3318956749435119</v>
+        <v>0.331895674943512</v>
       </c>
       <c r="C631" t="n">
-        <v>0.322436131011705</v>
+        <v>0.3224361310117052</v>
       </c>
       <c r="D631" t="n">
         <v>0.8763830156983143</v>
@@ -11192,7 +11192,7 @@
         <v>633</v>
       </c>
       <c r="B634" t="n">
-        <v>0.3305218686523743</v>
+        <v>0.3305218686523742</v>
       </c>
       <c r="C634" t="n">
         <v>0.3210980860195877</v>
@@ -11243,7 +11243,7 @@
         <v>636</v>
       </c>
       <c r="B637" t="n">
-        <v>0.3291529631242366</v>
+        <v>0.3291529631242367</v>
       </c>
       <c r="C637" t="n">
         <v>0.3197646138010993</v>
@@ -11416,7 +11416,7 @@
         <v>0.324627344635636</v>
       </c>
       <c r="C647" t="n">
-        <v>0.3153546484554783</v>
+        <v>0.3153546484554784</v>
       </c>
       <c r="D647" t="n">
         <v>0.8801482940392747</v>
@@ -11450,7 +11450,7 @@
         <v>0.3237294582143599</v>
       </c>
       <c r="C649" t="n">
-        <v>0.3144794245341171</v>
+        <v>0.3144794245341172</v>
       </c>
       <c r="D649" t="n">
         <v>0.8804379308347332</v>
@@ -11515,7 +11515,7 @@
         <v>652</v>
       </c>
       <c r="B653" t="n">
-        <v>0.3219412601696727</v>
+        <v>0.3219412601696728</v>
       </c>
       <c r="C653" t="n">
         <v>0.3127360692368106</v>
@@ -11532,7 +11532,7 @@
         <v>653</v>
       </c>
       <c r="B654" t="n">
-        <v>0.3214958180255004</v>
+        <v>0.3214958180255003</v>
       </c>
       <c r="C654" t="n">
         <v>0.3123017361210286</v>
@@ -11600,7 +11600,7 @@
         <v>657</v>
       </c>
       <c r="B658" t="n">
-        <v>0.3197206244124593</v>
+        <v>0.3197206244124594</v>
       </c>
       <c r="C658" t="n">
         <v>0.3105705661980085</v>
@@ -11617,7 +11617,7 @@
         <v>658</v>
       </c>
       <c r="B659" t="n">
-        <v>0.319278493213049</v>
+        <v>0.3192784932130491</v>
       </c>
       <c r="C659" t="n">
         <v>0.3101393368995231</v>
@@ -11688,7 +11688,7 @@
         <v>0.3175167732219226</v>
       </c>
       <c r="C663" t="n">
-        <v>0.3084208032255785</v>
+        <v>0.3084208032255784</v>
       </c>
       <c r="D663" t="n">
         <v>0.8831025893529514</v>
@@ -11702,7 +11702,7 @@
         <v>663</v>
       </c>
       <c r="B664" t="n">
-        <v>0.3170780662863686</v>
+        <v>0.3170780662863687</v>
       </c>
       <c r="C664" t="n">
         <v>0.3079927867297274</v>
@@ -11722,7 +11722,7 @@
         <v>0.3166400570932087</v>
       </c>
       <c r="C665" t="n">
-        <v>0.3075654252068123</v>
+        <v>0.3075654252068124</v>
       </c>
       <c r="D665" t="n">
         <v>0.8836818629438684</v>
@@ -11855,10 +11855,10 @@
         <v>672</v>
       </c>
       <c r="B673" t="n">
-        <v>0.3131615859919021</v>
+        <v>0.3131615859919022</v>
       </c>
       <c r="C673" t="n">
-        <v>0.3041705785618998</v>
+        <v>0.3041705785618999</v>
       </c>
       <c r="D673" t="n">
         <v>0.8848404101257024</v>
@@ -11872,7 +11872,7 @@
         <v>673</v>
       </c>
       <c r="B674" t="n">
-        <v>0.3127300351867161</v>
+        <v>0.3127300351867162</v>
       </c>
       <c r="C674" t="n">
         <v>0.3037492842066238</v>
@@ -11923,7 +11923,7 @@
         <v>676</v>
       </c>
       <c r="B677" t="n">
-        <v>0.3114398142527031</v>
+        <v>0.311439814252703</v>
       </c>
       <c r="C677" t="n">
         <v>0.3024895675823576</v>
@@ -12076,7 +12076,7 @@
         <v>685</v>
       </c>
       <c r="B686" t="n">
-        <v>0.3076098075161118</v>
+        <v>0.3076098075161117</v>
       </c>
       <c r="C686" t="n">
         <v>0.2987486647048303</v>
@@ -12178,7 +12178,7 @@
         <v>691</v>
       </c>
       <c r="B692" t="n">
-        <v>0.3050911603310362</v>
+        <v>0.3050911603310363</v>
       </c>
       <c r="C692" t="n">
         <v>0.2962873898048577</v>
@@ -12198,7 +12198,7 @@
         <v>0.3046741345096606</v>
       </c>
       <c r="C693" t="n">
-        <v>0.2958797668627853</v>
+        <v>0.2958797668627854</v>
       </c>
       <c r="D693" t="n">
         <v>0.8894166714939465</v>
@@ -12229,7 +12229,7 @@
         <v>694</v>
       </c>
       <c r="B695" t="n">
-        <v>0.3038424608287023</v>
+        <v>0.3038424608287024</v>
       </c>
       <c r="C695" t="n">
         <v>0.2950667620454303</v>
@@ -12331,7 +12331,7 @@
         <v>700</v>
       </c>
       <c r="B701" t="n">
-        <v>0.301366623112586</v>
+        <v>0.3013666231125861</v>
       </c>
       <c r="C701" t="n">
         <v>0.2926458329579564</v>
@@ -12348,7 +12348,7 @@
         <v>701</v>
       </c>
       <c r="B702" t="n">
-        <v>0.3009568028469194</v>
+        <v>0.3009568028469195</v>
       </c>
       <c r="C702" t="n">
         <v>0.2922450036902191</v>
@@ -12368,7 +12368,7 @@
         <v>0.3005477932711059</v>
       </c>
       <c r="C703" t="n">
-        <v>0.2918449392129309</v>
+        <v>0.291844939212931</v>
       </c>
       <c r="D703" t="n">
         <v>0.8921392573712564</v>
@@ -12385,7 +12385,7 @@
         <v>0.3001395961969435</v>
       </c>
       <c r="C704" t="n">
-        <v>0.2914456413230065</v>
+        <v>0.2914456413230067</v>
       </c>
       <c r="D704" t="n">
         <v>0.8924288941667149</v>
@@ -12419,7 +12419,7 @@
         <v>0.2993256465323402</v>
       </c>
       <c r="C706" t="n">
-        <v>0.2906493522406779</v>
+        <v>0.290649352240678</v>
       </c>
       <c r="D706" t="n">
         <v>0.8927764583212652</v>
@@ -12433,10 +12433,10 @@
         <v>706</v>
       </c>
       <c r="B707" t="n">
-        <v>0.2989198972986088</v>
+        <v>0.298919897298609</v>
       </c>
       <c r="C707" t="n">
-        <v>0.2902523643913602</v>
+        <v>0.2902523643913603</v>
       </c>
       <c r="D707" t="n">
         <v>0.8930081677576319</v>
@@ -12484,7 +12484,7 @@
         <v>709</v>
       </c>
       <c r="B710" t="n">
-        <v>0.2977075710349012</v>
+        <v>0.2977075710349013</v>
       </c>
       <c r="C710" t="n">
         <v>0.2890660466392506</v>
@@ -12603,7 +12603,7 @@
         <v>716</v>
       </c>
       <c r="B717" t="n">
-        <v>0.2949077006185866</v>
+        <v>0.2949077006185865</v>
       </c>
       <c r="C717" t="n">
         <v>0.2863252559918296</v>
@@ -12688,7 +12688,7 @@
         <v>721</v>
       </c>
       <c r="B722" t="n">
-        <v>0.2929327407462924</v>
+        <v>0.2929327407462923</v>
       </c>
       <c r="C722" t="n">
         <v>0.2843911219209118</v>
@@ -12708,7 +12708,7 @@
         <v>0.2925402570254285</v>
       </c>
       <c r="C723" t="n">
-        <v>0.2840066663893283</v>
+        <v>0.2840066663893284</v>
       </c>
       <c r="D723" t="n">
         <v>0.8959624630713086</v>
@@ -12739,7 +12739,7 @@
         <v>724</v>
       </c>
       <c r="B725" t="n">
-        <v>0.2917578047884492</v>
+        <v>0.2917578047884491</v>
       </c>
       <c r="C725" t="n">
         <v>0.28324013391376</v>
@@ -12807,7 +12807,7 @@
         <v>728</v>
       </c>
       <c r="B729" t="n">
-        <v>0.2902029818375773</v>
+        <v>0.2902029818375774</v>
       </c>
       <c r="C729" t="n">
         <v>0.2817166054942217</v>
@@ -12892,7 +12892,7 @@
         <v>733</v>
       </c>
       <c r="B734" t="n">
-        <v>0.28827840676303</v>
+        <v>0.2882784067630301</v>
       </c>
       <c r="C734" t="n">
         <v>0.279830131760182</v>
@@ -12909,7 +12909,7 @@
         <v>734</v>
       </c>
       <c r="B735" t="n">
-        <v>0.2878960238471446</v>
+        <v>0.2878960238471447</v>
       </c>
       <c r="C735" t="n">
         <v>0.2794552342271277</v>
@@ -12929,7 +12929,7 @@
         <v>0.2875144858706673</v>
       </c>
       <c r="C736" t="n">
-        <v>0.2790811368498758</v>
+        <v>0.2790811368498757</v>
       </c>
       <c r="D736" t="n">
         <v>0.897816138562243</v>
@@ -13133,7 +13133,7 @@
         <v>0.2830020136916498</v>
       </c>
       <c r="C748" t="n">
-        <v>0.2746544908596813</v>
+        <v>0.2746544908596814</v>
       </c>
       <c r="D748" t="n">
         <v>0.8999594508486358</v>
@@ -13283,7 +13283,7 @@
         <v>756</v>
       </c>
       <c r="B757" t="n">
-        <v>0.2796976150883394</v>
+        <v>0.2796976150883395</v>
       </c>
       <c r="C757" t="n">
         <v>0.2714103392354669</v>
@@ -13300,7 +13300,7 @@
         <v>757</v>
       </c>
       <c r="B758" t="n">
-        <v>0.2793346841830914</v>
+        <v>0.2793346841830915</v>
       </c>
       <c r="C758" t="n">
         <v>0.2710538884998612</v>
@@ -13368,7 +13368,7 @@
         <v>761</v>
       </c>
       <c r="B762" t="n">
-        <v>0.2778913930415591</v>
+        <v>0.2778913930415592</v>
       </c>
       <c r="C762" t="n">
         <v>0.2696360961057977</v>
@@ -13405,7 +13405,7 @@
         <v>0.2771748004840986</v>
       </c>
       <c r="C764" t="n">
-        <v>0.2689320016504203</v>
+        <v>0.2689320016504204</v>
       </c>
       <c r="D764" t="n">
         <v>0.9021027631350287</v>
@@ -13521,7 +13521,7 @@
         <v>770</v>
       </c>
       <c r="B771" t="n">
-        <v>0.2746931795888508</v>
+        <v>0.2746931795888507</v>
       </c>
       <c r="C771" t="n">
         <v>0.2664928241378113</v>
@@ -13538,10 +13538,10 @@
         <v>771</v>
       </c>
       <c r="B772" t="n">
-        <v>0.2743420129498319</v>
+        <v>0.274342012949832</v>
       </c>
       <c r="C772" t="n">
-        <v>0.2661475577123041</v>
+        <v>0.266147557712304</v>
       </c>
       <c r="D772" t="n">
         <v>0.9035509471123212</v>
@@ -13555,7 +13555,7 @@
         <v>772</v>
       </c>
       <c r="B773" t="n">
-        <v>0.273991681867447</v>
+        <v>0.2739916818674471</v>
       </c>
       <c r="C773" t="n">
         <v>0.2658030865124797</v>
@@ -13677,7 +13677,7 @@
         <v>0.2715626936369777</v>
       </c>
       <c r="C780" t="n">
-        <v>0.2634140012692688</v>
+        <v>0.2634140012692689</v>
       </c>
       <c r="D780" t="n">
         <v>0.9049412037305219</v>
@@ -13691,7 +13691,7 @@
         <v>780</v>
       </c>
       <c r="B781" t="n">
-        <v>0.2712190179916236</v>
+        <v>0.2712190179916237</v>
       </c>
       <c r="C781" t="n">
         <v>0.2630758684999588</v>
@@ -13728,7 +13728,7 @@
         <v>0.2705341497425705</v>
       </c>
       <c r="C783" t="n">
-        <v>0.2624019694593301</v>
+        <v>0.2624019694593302</v>
       </c>
       <c r="D783" t="n">
         <v>0.905114985807797</v>
@@ -13796,7 +13796,7 @@
         <v>0.2691743184271603</v>
       </c>
       <c r="C787" t="n">
-        <v>0.2610636150237577</v>
+        <v>0.2610636150237578</v>
       </c>
       <c r="D787" t="n">
         <v>0.9050570584487053</v>
@@ -13813,7 +13813,7 @@
         <v>0.2688364183421323</v>
       </c>
       <c r="C788" t="n">
-        <v>0.2607309889824726</v>
+        <v>0.2607309889824727</v>
       </c>
       <c r="D788" t="n">
         <v>0.9051729131668887</v>
@@ -13864,7 +13864,7 @@
         <v>0.2678276399557121</v>
       </c>
       <c r="C791" t="n">
-        <v>0.2597378070204001</v>
+        <v>0.2597378070204002</v>
       </c>
       <c r="D791" t="n">
         <v>0.9053466952441638</v>
@@ -13966,7 +13966,7 @@
         <v>0.265832132252773</v>
       </c>
       <c r="C797" t="n">
-        <v>0.2577724920092015</v>
+        <v>0.2577724920092016</v>
       </c>
       <c r="D797" t="n">
         <v>0.9066210971441812</v>
@@ -14014,7 +14014,7 @@
         <v>799</v>
       </c>
       <c r="B800" t="n">
-        <v>0.2648453405339055</v>
+        <v>0.2648453405339054</v>
       </c>
       <c r="C800" t="n">
         <v>0.2568003059907028</v>
@@ -14051,7 +14051,7 @@
         <v>0.2641915172771603</v>
       </c>
       <c r="C802" t="n">
-        <v>0.2561560413870264</v>
+        <v>0.2561560413870265</v>
       </c>
       <c r="D802" t="n">
         <v>0.9070845160169148</v>
@@ -14116,7 +14116,7 @@
         <v>805</v>
       </c>
       <c r="B806" t="n">
-        <v>0.2628935162546514</v>
+        <v>0.2628935162546515</v>
       </c>
       <c r="C806" t="n">
         <v>0.2548767357442177</v>
@@ -14133,7 +14133,7 @@
         <v>806</v>
       </c>
       <c r="B807" t="n">
-        <v>0.2625710179156109</v>
+        <v>0.262571017915611</v>
       </c>
       <c r="C807" t="n">
         <v>0.2545588243957725</v>
@@ -14167,7 +14167,7 @@
         <v>808</v>
       </c>
       <c r="B809" t="n">
-        <v>0.2619284142602691</v>
+        <v>0.2619284142602692</v>
       </c>
       <c r="C809" t="n">
         <v>0.253925291757877</v>
@@ -14204,7 +14204,7 @@
         <v>0.261288992279323</v>
       </c>
       <c r="C811" t="n">
-        <v>0.2532948047146769</v>
+        <v>0.253294804714677</v>
       </c>
       <c r="D811" t="n">
         <v>0.9080692811214737</v>
@@ -14269,7 +14269,7 @@
         <v>814</v>
       </c>
       <c r="B815" t="n">
-        <v>0.2600196491744532</v>
+        <v>0.2600196491744531</v>
       </c>
       <c r="C815" t="n">
         <v>0.2520429290454829</v>
@@ -14289,7 +14289,7 @@
         <v>0.2597042845415397</v>
       </c>
       <c r="C816" t="n">
-        <v>0.2517318484888876</v>
+        <v>0.2517318484888877</v>
       </c>
       <c r="D816" t="n">
         <v>0.9087064820714824</v>
@@ -14303,7 +14303,7 @@
         <v>816</v>
       </c>
       <c r="B817" t="n">
-        <v>0.2593897055095745</v>
+        <v>0.2593897055095744</v>
       </c>
       <c r="C817" t="n">
         <v>0.2514215207836671</v>
@@ -14320,7 +14320,7 @@
         <v>817</v>
       </c>
       <c r="B818" t="n">
-        <v>0.2590759106316352</v>
+        <v>0.2590759106316353</v>
       </c>
       <c r="C818" t="n">
         <v>0.2511119446647195</v>
@@ -14388,7 +14388,7 @@
         <v>821</v>
       </c>
       <c r="B822" t="n">
-        <v>0.2578285433622943</v>
+        <v>0.2578285433622944</v>
       </c>
       <c r="C822" t="n">
         <v>0.2498811303901685</v>
@@ -14405,7 +14405,7 @@
         <v>822</v>
       </c>
       <c r="B823" t="n">
-        <v>0.2575186471939728</v>
+        <v>0.2575186471939729</v>
       </c>
       <c r="C823" t="n">
         <v>0.2495752928690105</v>
@@ -14422,7 +14422,7 @@
         <v>823</v>
       </c>
       <c r="B824" t="n">
-        <v>0.2572095262868395</v>
+        <v>0.2572095262868396</v>
       </c>
       <c r="C824" t="n">
         <v>0.2492701991316766</v>
@@ -14473,7 +14473,7 @@
         <v>826</v>
       </c>
       <c r="B827" t="n">
-        <v>0.2562867999317467</v>
+        <v>0.2562867999317466</v>
       </c>
       <c r="C827" t="n">
         <v>0.2483593672354472</v>
@@ -14490,7 +14490,7 @@
         <v>827</v>
       </c>
       <c r="B828" t="n">
-        <v>0.2559807648239934</v>
+        <v>0.2559807648239935</v>
       </c>
       <c r="C828" t="n">
         <v>0.2480572352009029</v>
@@ -14507,7 +14507,7 @@
         <v>828</v>
       </c>
       <c r="B829" t="n">
-        <v>0.255675497310821</v>
+        <v>0.2556754973108211</v>
       </c>
       <c r="C829" t="n">
         <v>0.2477558401891539</v>
@@ -14609,7 +14609,7 @@
         <v>834</v>
       </c>
       <c r="B835" t="n">
-        <v>0.253859923849138</v>
+        <v>0.2538599238491379</v>
       </c>
       <c r="C835" t="n">
         <v>0.2459628698206688</v>
@@ -14626,7 +14626,7 @@
         <v>835</v>
       </c>
       <c r="B836" t="n">
-        <v>0.2535599853992724</v>
+        <v>0.2535599853992723</v>
       </c>
       <c r="C836" t="n">
         <v>0.2456665949100194</v>
@@ -14643,7 +14643,7 @@
         <v>836</v>
       </c>
       <c r="B837" t="n">
-        <v>0.2532608018524442</v>
+        <v>0.2532608018524441</v>
       </c>
       <c r="C837" t="n">
         <v>0.2453710457671867</v>
@@ -14677,7 +14677,7 @@
         <v>838</v>
       </c>
       <c r="B839" t="n">
-        <v>0.252664692982401</v>
+        <v>0.2526646929824009</v>
       </c>
       <c r="C839" t="n">
         <v>0.2447821190115788</v>
@@ -14694,7 +14694,7 @@
         <v>839</v>
       </c>
       <c r="B840" t="n">
-        <v>0.2523677643994903</v>
+        <v>0.2523677643994904</v>
       </c>
       <c r="C840" t="n">
         <v>0.2444887384942008</v>
@@ -14745,7 +14745,7 @@
         <v>842</v>
       </c>
       <c r="B843" t="n">
-        <v>0.2514814623639294</v>
+        <v>0.2514814623639295</v>
       </c>
       <c r="C843" t="n">
         <v>0.2436129108104582</v>
@@ -14881,7 +14881,7 @@
         <v>850</v>
       </c>
       <c r="B851" t="n">
-        <v>0.2491505782267626</v>
+        <v>0.2491505782267627</v>
       </c>
       <c r="C851" t="n">
         <v>0.2413087435927692</v>
@@ -14915,7 +14915,7 @@
         <v>852</v>
       </c>
       <c r="B853" t="n">
-        <v>0.248575190653513</v>
+        <v>0.2485751906535129</v>
       </c>
       <c r="C853" t="n">
         <v>0.2407397667030815</v>
@@ -14983,7 +14983,7 @@
         <v>856</v>
       </c>
       <c r="B857" t="n">
-        <v>0.2474331202476777</v>
+        <v>0.2474331202476778</v>
       </c>
       <c r="C857" t="n">
         <v>0.2396102049959778</v>
@@ -15000,7 +15000,7 @@
         <v>857</v>
       </c>
       <c r="B858" t="n">
-        <v>0.2471494060943716</v>
+        <v>0.2471494060943715</v>
       </c>
       <c r="C858" t="n">
         <v>0.2393295538639872</v>
@@ -15054,7 +15054,7 @@
         <v>0.2463025642079766</v>
       </c>
       <c r="C861" t="n">
-        <v>0.2384917497526904</v>
+        <v>0.2384917497526905</v>
       </c>
       <c r="D861" t="n">
         <v>0.9135723802351851</v>
@@ -15102,7 +15102,7 @@
         <v>863</v>
       </c>
       <c r="B864" t="n">
-        <v>0.2454621366034439</v>
+        <v>0.245462136603444</v>
       </c>
       <c r="C864" t="n">
         <v>0.2376601364690935</v>
@@ -15136,7 +15136,7 @@
         <v>865</v>
       </c>
       <c r="B866" t="n">
-        <v>0.2449053916948402</v>
+        <v>0.2449053916948401</v>
       </c>
       <c r="C866" t="n">
         <v>0.2371091458220953</v>
@@ -15224,7 +15224,7 @@
         <v>0.2435258173264377</v>
       </c>
       <c r="C871" t="n">
-        <v>0.2357435397193481</v>
+        <v>0.2357435397193482</v>
       </c>
       <c r="D871" t="n">
         <v>0.9142675085442855</v>
@@ -15340,7 +15340,7 @@
         <v>877</v>
       </c>
       <c r="B878" t="n">
-        <v>0.2416235569949629</v>
+        <v>0.241623556994963</v>
       </c>
       <c r="C878" t="n">
         <v>0.2338598643616772</v>
@@ -15357,7 +15357,7 @@
         <v>878</v>
       </c>
       <c r="B879" t="n">
-        <v>0.241354550264849</v>
+        <v>0.2413545502648491</v>
       </c>
       <c r="C879" t="n">
         <v>0.2335934228949038</v>
@@ -15408,7 +15408,7 @@
         <v>881</v>
       </c>
       <c r="B882" t="n">
-        <v>0.2405516078650457</v>
+        <v>0.2405516078650458</v>
       </c>
       <c r="C882" t="n">
         <v>0.2327980450518504</v>
@@ -15717,7 +15717,7 @@
         <v>0.235859913587212</v>
       </c>
       <c r="C900" t="n">
-        <v>0.2281478083824812</v>
+        <v>0.2281478083824813</v>
       </c>
       <c r="D900" t="n">
         <v>0.9169321670625036</v>
@@ -15785,7 +15785,7 @@
         <v>0.23484597854026</v>
       </c>
       <c r="C904" t="n">
-        <v>0.22714222334855</v>
+        <v>0.2271422233485501</v>
       </c>
       <c r="D904" t="n">
         <v>0.9173955859352372</v>
@@ -16020,7 +16020,7 @@
         <v>917</v>
       </c>
       <c r="B918" t="n">
-        <v>0.231376565151295</v>
+        <v>0.2313765651512951</v>
       </c>
       <c r="C918" t="n">
         <v>0.2236997669031883</v>
@@ -16071,7 +16071,7 @@
         <v>920</v>
       </c>
       <c r="B921" t="n">
-        <v>0.2306488598557022</v>
+        <v>0.2306488598557023</v>
       </c>
       <c r="C921" t="n">
         <v>0.2229774015607971</v>
@@ -16105,7 +16105,7 @@
         <v>922</v>
       </c>
       <c r="B923" t="n">
-        <v>0.2301667527315658</v>
+        <v>0.2301667527315659</v>
       </c>
       <c r="C923" t="n">
         <v>0.222498772650572</v>
@@ -16193,7 +16193,7 @@
         <v>0.2289719852468556</v>
       </c>
       <c r="C928" t="n">
-        <v>0.2213124213493085</v>
+        <v>0.2213124213493086</v>
       </c>
       <c r="D928" t="n">
         <v>0.9190754793488964</v>
@@ -16207,7 +16207,7 @@
         <v>928</v>
       </c>
       <c r="B929" t="n">
-        <v>0.2287348176153287</v>
+        <v>0.2287348176153286</v>
       </c>
       <c r="C929" t="n">
         <v>0.2210768899794076</v>
@@ -16292,7 +16292,7 @@
         <v>933</v>
       </c>
       <c r="B934" t="n">
-        <v>0.2275578115804077</v>
+        <v>0.2275578115804078</v>
       </c>
       <c r="C934" t="n">
         <v>0.2199078365179202</v>
@@ -16326,7 +16326,7 @@
         <v>935</v>
       </c>
       <c r="B936" t="n">
-        <v>0.2270910979626888</v>
+        <v>0.2270910979626889</v>
       </c>
       <c r="C936" t="n">
         <v>0.2194441992233465</v>
@@ -16380,7 +16380,7 @@
         <v>0.2263953645363437</v>
       </c>
       <c r="C939" t="n">
-        <v>0.2187529707709792</v>
+        <v>0.2187529707709793</v>
       </c>
       <c r="D939" t="n">
         <v>0.9194809708625383</v>
@@ -16414,7 +16414,7 @@
         <v>0.2259344132052248</v>
       </c>
       <c r="C941" t="n">
-        <v>0.2182949509700321</v>
+        <v>0.218294950970032</v>
       </c>
       <c r="D941" t="n">
         <v>0.9200023170943636</v>
@@ -16666,7 +16666,7 @@
         <v>955</v>
       </c>
       <c r="B956" t="n">
-        <v>0.2225490150043468</v>
+        <v>0.2225490150043467</v>
       </c>
       <c r="C956" t="n">
         <v>0.2149297942045093</v>
@@ -16836,7 +16836,7 @@
         <v>965</v>
       </c>
       <c r="B966" t="n">
-        <v>0.220360488454333</v>
+        <v>0.2203604884543331</v>
       </c>
       <c r="C966" t="n">
         <v>0.2127531581888555</v>
@@ -16873,7 +16873,7 @@
         <v>0.2199291677509322</v>
       </c>
       <c r="C968" t="n">
-        <v>0.2123240713651619</v>
+        <v>0.212324071365162</v>
       </c>
       <c r="D968" t="n">
         <v>0.9224352661762151</v>
@@ -16975,7 +16975,7 @@
         <v>0.2186477356936556</v>
       </c>
       <c r="C974" t="n">
-        <v>0.2110490646780591</v>
+        <v>0.211049064678059</v>
       </c>
       <c r="D974" t="n">
         <v>0.9229566124080403</v>
@@ -17023,7 +17023,7 @@
         <v>976</v>
       </c>
       <c r="B977" t="n">
-        <v>0.2180139865223943</v>
+        <v>0.2180139865223942</v>
       </c>
       <c r="C977" t="n">
         <v>0.2104183768140386</v>
@@ -17057,7 +17057,7 @@
         <v>978</v>
       </c>
       <c r="B979" t="n">
-        <v>0.2175940374983418</v>
+        <v>0.2175940374983419</v>
       </c>
       <c r="C979" t="n">
         <v>0.2100004140490851</v>
@@ -17247,7 +17247,7 @@
         <v>0.2153201749397613</v>
       </c>
       <c r="C990" t="n">
-        <v>0.2077367239438956</v>
+        <v>0.2077367239438957</v>
       </c>
       <c r="D990" t="n">
         <v>0.9249840699762498</v>
@@ -17329,7 +17329,7 @@
         <v>994</v>
       </c>
       <c r="B995" t="n">
-        <v>0.2143062793506044</v>
+        <v>0.2143062793506043</v>
       </c>
       <c r="C995" t="n">
         <v>0.2067270490377965</v>
@@ -17400,7 +17400,7 @@
         <v>0.2135038298940809</v>
       </c>
       <c r="C999" t="n">
-        <v>0.2059278031062427</v>
+        <v>0.2059278031062428</v>
       </c>
       <c r="D999" t="n">
         <v>0.9252157794126166</v>
@@ -17431,7 +17431,7 @@
         <v>1000</v>
       </c>
       <c r="B1001" t="n">
-        <v>0.2131054601448705</v>
+        <v>0.2131054601448706</v>
       </c>
       <c r="C1001" t="n">
         <v>0.2055309789219739</v>
